--- a/data/trans_orig/IP42E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP42E-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63492</t>
+          <t>63581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76738</t>
+          <t>76335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72852</t>
+          <t>72388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86248</t>
+          <t>85458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140488</t>
+          <t>139471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160084</t>
+          <t>158879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>15274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26386</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>150761</t>
+          <t>150216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171028</t>
+          <t>170122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>159365</t>
+          <t>159403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177662</t>
+          <t>178199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>314557</t>
+          <t>316509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>342234</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21513</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31433</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49295</t>
+          <t>49472</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66702</t>
+          <t>66627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79919</t>
+          <t>80681</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77579</t>
+          <t>77889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>93302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>149510</t>
+          <t>148221</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>170205</t>
+          <t>168410</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33845</t>
+          <t>34622</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>104788</t>
+          <t>103708</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122388</t>
+          <t>121795</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106341</t>
+          <t>105688</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>123137</t>
+          <t>122689</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>215341</t>
+          <t>215452</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>241143</t>
+          <t>239958</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30465</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56286</t>
+          <t>55795</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>403201</t>
+          <t>403273</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>434977</t>
+          <t>434901</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>430633</t>
+          <t>432587</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>463716</t>
+          <t>466291</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>843521</t>
+          <t>844000</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>888914</t>
+          <t>889716</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>35685</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>58731</t>
+          <t>56820</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -4591,12 +4591,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23889</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>41257</t>
+          <t>41278</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>45562</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>70344</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4945,82 +4945,82 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>10784</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>6450</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>17172</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>24311</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>17322</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>33660</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>10784</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>6630</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>17699</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>24311</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>17628</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>33225</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>47489</t>
+          <t>47640</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>71422</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>55938</t>
+          <t>54676</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>80261</t>
+          <t>80227</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>109554</t>
+          <t>111321</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>145346</t>
+          <t>145206</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94440</t>
+          <t>94487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108185</t>
+          <t>108635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91828</t>
+          <t>92444</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107934</t>
+          <t>107080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>190604</t>
+          <t>192156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211489</t>
+          <t>212757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -6070,12 +6070,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20577</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35338</t>
+          <t>34364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132867</t>
+          <t>131961</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>152137</t>
+          <t>152574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146649</t>
+          <t>146760</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168140</t>
+          <t>169096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>316300</t>
+          <t>314977</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>19614</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33892</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -6787,12 +6787,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30252</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7063,12 +7063,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -7091,12 +7091,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33946</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31920</t>
+          <t>31626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>61935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -7321,12 +7321,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85058</t>
+          <t>85059</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101156</t>
+          <t>100698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92018</t>
+          <t>93212</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107947</t>
+          <t>108855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182060</t>
+          <t>182425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204089</t>
+          <t>205354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>13452</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7484,12 +7484,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7519,12 +7519,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7602,42 +7602,42 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2680</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6163</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>2,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2680</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6598</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -7999,12 +7999,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>37213</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -8229,12 +8229,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94447</t>
+          <t>94460</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>111895</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>91863</t>
+          <t>91311</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109310</t>
+          <t>109032</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>191259</t>
+          <t>191222</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>215404</t>
+          <t>215369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -8342,12 +8342,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8357,12 +8357,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -8455,12 +8455,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8681,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8907,12 +8907,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28902</t>
+          <t>28404</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8977,12 +8977,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46988</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>425042</t>
+          <t>424532</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>459450</t>
+          <t>458409</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>441398</t>
+          <t>443122</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>477129</t>
+          <t>478962</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>875951</t>
+          <t>876259</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>925852</t>
+          <t>925533</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -9250,12 +9250,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>36956</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46905</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>73182</t>
+          <t>70215</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -9363,12 +9363,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>30550</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>43868</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9772,12 +9772,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>57906</t>
+          <t>56052</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>83092</t>
+          <t>82234</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>59339</t>
+          <t>58109</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>84966</t>
+          <t>84994</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>123732</t>
+          <t>121760</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>161800</t>
+          <t>157282</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -10277,12 +10277,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84248</t>
+          <t>83820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95721</t>
+          <t>95697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80350</t>
+          <t>79914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91072</t>
+          <t>90923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10347,12 +10347,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166480</t>
+          <t>168838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>183788</t>
+          <t>183592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,54%</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10729,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -10955,12 +10955,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10990,12 +10990,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27087</t>
+          <t>26709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140667</t>
+          <t>140532</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154010</t>
+          <t>152985</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144244</t>
+          <t>143728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159782</t>
+          <t>160050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11255,12 +11255,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>290110</t>
+          <t>290196</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>310581</t>
+          <t>310641</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11348,47 +11348,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>10459</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>6249</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>16891</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>10459</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>6146</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>17354</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11652,12 +11652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -11863,12 +11863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15994</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11878,12 +11878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18442</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33916</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11948,12 +11948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91836</t>
+          <t>91575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107038</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103664</t>
+          <t>103686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>118442</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200456</t>
+          <t>199876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221520</t>
+          <t>220841</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -12206,12 +12206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12221,12 +12221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22912</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12786,12 +12786,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>21667</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>37458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -13001,12 +13001,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>93125</t>
+          <t>92300</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>108294</t>
+          <t>108127</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13016,12 +13016,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93623</t>
+          <t>93294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>108462</t>
+          <t>107990</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>191689</t>
+          <t>191785</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>212162</t>
+          <t>212046</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -13114,12 +13114,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13129,12 +13129,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13164,12 +13164,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -13453,12 +13453,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13468,12 +13468,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -13566,12 +13566,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13581,12 +13581,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -13636,12 +13636,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -13679,12 +13679,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13694,12 +13694,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>18482</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13729,12 +13729,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13749,12 +13749,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37205</t>
+          <t>36512</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13764,12 +13764,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -13909,12 +13909,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>424946</t>
+          <t>424933</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>451894</t>
+          <t>453920</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13924,12 +13924,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>436857</t>
+          <t>436492</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>465309</t>
+          <t>465351</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>871915</t>
+          <t>870386</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>909984</t>
+          <t>909948</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -14022,12 +14022,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14037,12 +14037,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14057,12 +14057,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>27208</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14072,12 +14072,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14092,12 +14092,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>40826</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14107,12 +14107,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14205,12 +14205,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14283,12 +14283,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>523</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -14361,12 +14361,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14396,12 +14396,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14411,12 +14411,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>33214</t>
+          <t>33527</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -14474,12 +14474,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14509,12 +14509,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14544,12 +14544,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -14587,12 +14587,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>42998</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>65381</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>59829</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14637,12 +14637,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>86954</t>
+          <t>85453</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>117847</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14672,12 +14672,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -17808,7 +17808,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -18751,12 +18751,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -18766,12 +18766,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -19138,7 +19138,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -19399,7 +19399,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19449,7 +19449,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
